--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487903_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487903_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3389</v>
+        <v>6.7084</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4153</v>
+        <v>8.403</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0764</v>
+        <v>-1.6947</v>
       </c>
       <c r="G2" t="n">
         <v>1.4475</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8919</v>
+        <v>0.4776</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1744</v>
+        <v>-0.1866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2825</v>
+        <v>0.6642</v>
       </c>
       <c r="V2" t="n">
         <v>4.7833</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3443</v>
+        <v>5.5954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5776</v>
+        <v>4.5458</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7667</v>
+        <v>1.0496</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7983</v>
+        <v>1.7575</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4644</v>
+        <v>-1.4396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3339</v>
+        <v>3.1971</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8718</v>
+        <v>4.3947</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7543</v>
+        <v>0.3853</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>4.0094</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0735</v>
+        <v>-2.6373</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2899</v>
+        <v>-1.825</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2164</v>
+        <v>-0.8123</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>2.9137</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7701</v>
+        <v>1.0631</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5559</v>
+        <v>-0.1028</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2142</v>
+        <v>1.1659</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2241</v>
+        <v>1.9423</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.769</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5449000000000001</v>
+        <v>-0.3927</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2531</v>
+        <v>3.1526</v>
       </c>
       <c r="E4" t="n">
-        <v>3.409</v>
+        <v>1.3206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8441</v>
+        <v>1.8319</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7575</v>
+        <v>-0.5229</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4396</v>
+        <v>-0.998</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1971</v>
+        <v>0.4752</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3947</v>
+        <v>1.7266</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3853</v>
+        <v>0.831</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0094</v>
+        <v>0.8956</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6373</v>
+        <v>-2.2495</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.825</v>
+        <v>-1.8291</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8123</v>
+        <v>-0.4204</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9137</v>
+        <v>3.3299</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2792</v>
+        <v>1.4149</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2396</v>
+        <v>0.2777</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9604</v>
+        <v>1.1372</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9423</v>
+        <v>1.0119</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3351</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3927</v>
+        <v>-0.3856</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5943</v>
+        <v>2.9269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2321</v>
+        <v>-0.4287</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3622</v>
+        <v>3.3557</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5229</v>
+        <v>2.7983</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.998</v>
+        <v>2.4644</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4752</v>
+        <v>0.3339</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7266</v>
+        <v>2.8718</v>
       </c>
       <c r="K5" t="n">
-        <v>0.831</v>
+        <v>2.7543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8956</v>
+        <v>0.1176</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2495</v>
+        <v>-0.0735</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8291</v>
+        <v>-0.2899</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4204</v>
+        <v>0.2164</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3299</v>
+        <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8566</v>
+        <v>1.3528</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1891</v>
+        <v>0.5496</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6675</v>
+        <v>0.8032</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0119</v>
+        <v>-1.2241</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3975</v>
+        <v>-1.769</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3856</v>
+        <v>0.5449000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1512</v>
+        <v>2.0882</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5429</v>
+        <v>1.2744</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6083</v>
+        <v>0.8138</v>
       </c>
       <c r="G6" t="n">
         <v>0.479</v>
@@ -922,13 +922,13 @@
         <v>3.1218</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4351</v>
+        <v>1.3722</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5252</v>
+        <v>0.2063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9604</v>
+        <v>1.1659</v>
       </c>
       <c r="V6" t="n">
         <v>0.237</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3423</v>
+        <v>0.6452</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5499</v>
+        <v>-1.247</v>
       </c>
       <c r="F7" t="n">
         <v>1.8923</v>
@@ -1000,10 +1000,10 @@
         <v>2.7055</v>
       </c>
       <c r="S7" t="n">
-        <v>0.702</v>
+        <v>1.0049</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1338</v>
+        <v>0.1691</v>
       </c>
       <c r="U7" t="n">
         <v>0.8358</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3255</v>
+        <v>-0.1196</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3951</v>
+        <v>1.7958</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0697</v>
+        <v>-1.9154</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6197</v>
+        <v>-1.2904</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9479</v>
+        <v>-0.6891</v>
       </c>
       <c r="J8" t="n">
-        <v>1.728</v>
+        <v>2.0367</v>
       </c>
       <c r="K8" t="n">
-        <v>1.541</v>
+        <v>0.8399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.187</v>
+        <v>1.1969</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3477</v>
+        <v>-3.3271</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2129</v>
+        <v>-1.4412</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1348</v>
+        <v>-1.8859</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1056</v>
+        <v>0.0442</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7484</v>
+        <v>-0.2409</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3573</v>
+        <v>0.2851</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7442</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7442</v>
+        <v>-0.7465000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1593</v>
+        <v>-0.3238</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9029</v>
+        <v>0.0356</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0622</v>
+        <v>-0.3595</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2904</v>
+        <v>-0.7855</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.5756</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6891</v>
+        <v>-0.2098</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0367</v>
+        <v>0.0392</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8399</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1969</v>
+        <v>0.0392</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3271</v>
+        <v>-0.8247</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4412</v>
+        <v>-0.5756</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8859</v>
+        <v>-0.249</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8731</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.08160000000000001</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1305</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.8731</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.1338</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1383</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.7465000000000001</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.7465000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3532</v>
+        <v>-1.8472</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0356</v>
+        <v>0.1326</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3888</v>
+        <v>-1.9798</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7855</v>
+        <v>-1.6197</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5756</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2098</v>
+        <v>-0.9479</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0392</v>
+        <v>1.728</v>
       </c>
       <c r="K10" t="n">
+        <v>1.541</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-3.3477</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-2.2129</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.1348</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4162</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.9329</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4471</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.7442</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.0392</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.8247</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.5756</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.249</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.6244</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4162</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.1109</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.1305</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1675</v>
-      </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3282</v>
+        <v>-4.3473</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0268</v>
+        <v>-1.134</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3014</v>
+        <v>-3.2133</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4504</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1611</v>
+        <v>0.142</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0619</v>
+        <v>-0.0452</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0992</v>
+        <v>0.1873</v>
       </c>
       <c r="V11" t="n">
         <v>-2.374</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8643</v>
+        <v>-4.8555</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9304</v>
+        <v>-3.7161</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9339</v>
+        <v>-1.1394</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9723</v>
@@ -1390,13 +1390,13 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0189</v>
+        <v>-0.0101</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3725</v>
+        <v>0.167</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.644600000000001</v>
+        <v>9.623299999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0034</v>
+        <v>10.982</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3588</v>
+        <v>-1.358800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-2.836800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.979800000000001</v>
+        <v>-4.979799999999999</v>
       </c>
       <c r="I13" t="n">
         <v>2.1432</v>
       </c>
       <c r="J13" t="n">
-        <v>20.3926</v>
+        <v>20.39260000000001</v>
       </c>
       <c r="K13" t="n">
         <v>8.493300000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-13.4732</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.755999999999998</v>
+        <v>-9.756</v>
       </c>
       <c r="P13" t="n">
         <v>1.0406</v>
@@ -1468,13 +1468,13 @@
         <v>21.8524</v>
       </c>
       <c r="S13" t="n">
-        <v>7.7341</v>
+        <v>8.712899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1735</v>
+        <v>0.8053999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>7.907699999999999</v>
+        <v>7.907599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.7065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.721</v>
+        <v>6.4362</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4198</v>
+        <v>3.6342</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3011</v>
+        <v>2.802</v>
       </c>
       <c r="G14" t="n">
         <v>1.0769</v>
@@ -1546,13 +1546,13 @@
         <v>2.7055</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5964</v>
+        <v>0.3116</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8482</v>
+        <v>-0.6338</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4445</v>
+        <v>0.9454</v>
       </c>
       <c r="V14" t="n">
         <v>2.3421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1348</v>
+        <v>2.2508</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6184</v>
+        <v>1.9398</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5165</v>
+        <v>0.3109</v>
       </c>
       <c r="G15" t="n">
         <v>2.1814</v>
@@ -1624,13 +1624,13 @@
         <v>3.3299</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5253</v>
+        <v>-1.4093</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7616</v>
+        <v>-1.4401</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2363</v>
+        <v>0.0308</v>
       </c>
       <c r="V15" t="n">
         <v>0.23</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9101</v>
+        <v>2.2491</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3316</v>
+        <v>3.2086</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4214</v>
+        <v>-0.9596</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6273</v>
+        <v>1.5149</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1556</v>
+        <v>0.8487</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5282</v>
+        <v>0.6662</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0931</v>
+        <v>4.0419</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0251</v>
+        <v>0.955</v>
       </c>
       <c r="L16" t="n">
-        <v>2.068</v>
+        <v>3.0869</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4658</v>
+        <v>-2.527</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1304</v>
+        <v>-0.1063</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5962</v>
+        <v>-2.4207</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2893</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3299</v>
+        <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7222</v>
+        <v>-0.1491</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.721</v>
+        <v>-0.5034</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0012</v>
+        <v>0.3543</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2843</v>
+        <v>0.467</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="X16" t="n">
         <v>-1.2843</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.565</v>
+        <v>1.7355</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9943</v>
+        <v>2.0101</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4293</v>
+        <v>-0.2746</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5149</v>
+        <v>1.6273</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8487</v>
+        <v>2.1556</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6662</v>
+        <v>-0.5282</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0419</v>
+        <v>4.0931</v>
       </c>
       <c r="K17" t="n">
-        <v>0.955</v>
+        <v>2.0251</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0869</v>
+        <v>2.068</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.527</v>
+        <v>-2.4658</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1063</v>
+        <v>0.1304</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4207</v>
+        <v>-2.5962</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4974</v>
+        <v>3.3299</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8331</v>
+        <v>-0.8969</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7177</v>
+        <v>-1.0424</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1155</v>
+        <v>0.1456</v>
       </c>
       <c r="V17" t="n">
-        <v>0.467</v>
+        <v>-1.2843</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7513</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-1.2843</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7423</v>
+        <v>-0.9169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7075</v>
+        <v>0.386</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4498</v>
+        <v>-1.303</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5545</v>
@@ -1858,13 +1858,13 @@
         <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0202</v>
+        <v>-0.1949</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3229</v>
+        <v>0.0014</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3431</v>
+        <v>-0.1964</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5838</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2375</v>
+        <v>-2.0819</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6431</v>
+        <v>-1.4288</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5944</v>
+        <v>-0.6531</v>
       </c>
       <c r="G19" t="n">
         <v>1.2339</v>
@@ -1936,13 +1936,13 @@
         <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5984</v>
+        <v>-1.4428</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6311</v>
+        <v>-1.4168</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0327</v>
+        <v>-0.026</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4801</v>
+        <v>-2.7913</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5755</v>
+        <v>-1.0042</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9046</v>
+        <v>-1.7872</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2527</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2355</v>
+        <v>-0.5467</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1924</v>
+        <v>-0.2362</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.428</v>
+        <v>-0.3105</v>
       </c>
       <c r="V20" t="n">
         <v>-1.9919</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9452</v>
+        <v>-4.2667</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3806</v>
+        <v>-1.7021</v>
       </c>
       <c r="F21" t="n">
         <v>-2.5646</v>
@@ -2092,10 +2092,10 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2981</v>
+        <v>-0.0233</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1272</v>
+        <v>-0.1943</v>
       </c>
       <c r="U21" t="n">
         <v>0.171</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7834</v>
+        <v>-5.5984</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8946</v>
+        <v>-2.6803</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8888</v>
+        <v>-2.9181</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1746</v>
@@ -2170,13 +2170,13 @@
         <v>3.1218</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8926</v>
+        <v>-1.7077</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.6311</v>
+        <v>-1.4168</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2616</v>
+        <v>-0.2909</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5944</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.787</v>
+        <v>-5.6608</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2188</v>
+        <v>-3.0045</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5682</v>
+        <v>-2.6563</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4238</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8013</v>
+        <v>-1.6751</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2396</v>
+        <v>-1.0253</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5617</v>
+        <v>-0.6498</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9376</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.644600000000001</v>
+        <v>-8.644399999999997</v>
       </c>
       <c r="E24" t="n">
-        <v>1.359</v>
+        <v>1.3588</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.0035</v>
+        <v>-10.0036</v>
       </c>
       <c r="G24" t="n">
         <v>2.8367</v>
@@ -2326,13 +2326,13 @@
         <v>20.8118</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.7341</v>
+        <v>-7.7342</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.9078</v>
+        <v>-7.9077</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1733999999999999</v>
+        <v>0.1735000000000003</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7067</v>
